--- a/docs/MML.xlsx
+++ b/docs/MML.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maczoo/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maczoo/Desktop/eunseo/dev/mammoth_menu_learner/mammoth-menu-learner/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CD6C2D-13AB-5C44-8ED9-BA6D2D652830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8324D3-2992-3642-B15D-096AAC563BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{6AB7D526-CE02-4D48-875F-4A9BFDBFB343}"/>
+    <workbookView minimized="1" xWindow="12900" yWindow="-1880" windowWidth="29400" windowHeight="16540" activeTab="2" xr2:uid="{6AB7D526-CE02-4D48-875F-4A9BFDBFB343}"/>
   </bookViews>
   <sheets>
     <sheet name="매머드 익스프레스" sheetId="1" r:id="rId1"/>
     <sheet name="용량" sheetId="2" r:id="rId2"/>
+    <sheet name="주문 받아 본 적 있는 메뉴" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="245">
   <si>
     <t>카테고리</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -957,6 +958,46 @@
   </si>
   <si>
     <t>티백은 2분 간 우린다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카페라떼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바닐라라떼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>곡물라떼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>곡물쉐이크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인크레더불</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>꿀커피</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아샷추</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자허블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사과모과차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌체 라떼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6934,4 +6975,202 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61FA90B0-D3B2-3045-924D-37872FF0621D}">
+  <dimension ref="B2:C24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15" t="s">
+        <v>243</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" t="s">
+        <v>244</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/MML.xlsx
+++ b/docs/MML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maczoo/Desktop/eunseo/dev/mammoth_menu_learner/mammoth-menu-learner/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CE90FC-9E91-F940-872D-648FA695AE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E81D8D-61BA-E14A-8F4B-EBBE09BC939C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="6" xr2:uid="{6AB7D526-CE02-4D48-875F-4A9BFDBFB343}"/>
   </bookViews>
